--- a/RegistrosPOST.xlsx
+++ b/RegistrosPOST.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luli/Desktop/StroopTest/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luli/Desktop/Cognitio/StroopTest/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79ACD1B-AF9F-F945-8424-0FC04B19A4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66779DD9-A5E6-CB49-AEA9-A73467AE4D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="500" windowWidth="27640" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="0" windowWidth="27640" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/RegistrosPOST.xlsx
+++ b/RegistrosPOST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luli/Desktop/Cognitio/StroopTest/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66779DD9-A5E6-CB49-AEA9-A73467AE4D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F96945-B7FC-D24B-BD8C-7C488E4338BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="0" windowWidth="27640" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>SUJETO</t>
   </si>
@@ -61,19 +61,22 @@
     <t>PC</t>
   </si>
   <si>
+    <t>PCcorregido</t>
+  </si>
+  <si>
+    <t>TPC</t>
+  </si>
+  <si>
+    <t>PC'</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
     <t>Pccorregido</t>
-  </si>
-  <si>
-    <t>TPC</t>
-  </si>
-  <si>
-    <t>PC'</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>TI</t>
   </si>
   <si>
     <t>DifP</t>
@@ -673,7 +676,7 @@
         <v>12</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>14</v>
@@ -688,22 +691,22 @@
         <v>17</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
